--- a/Proyectos/Fundamentos-de-Construccion/Solucion/MEMORIAS DE CALCULO -FORMATO PROFESOR- DILIGENCIADO.xlsx
+++ b/Proyectos/Fundamentos-de-Construccion/Solucion/MEMORIAS DE CALCULO -FORMATO PROFESOR- DILIGENCIADO.xlsx
@@ -6698,7 +6698,7 @@
       <c r="J17" s="45" t="n"/>
       <c r="K17" s="38" t="inlineStr">
         <is>
-          <t>Columnetas c/3m (58 und x H=2.90)</t>
+          <t>Columnetas c/1.5m (116 und x H=2.90)</t>
         </is>
       </c>
       <c r="L17" s="42" t="n"/>
@@ -6713,11 +6713,11 @@
         <v>2.9</v>
       </c>
       <c r="Q17" s="39" t="n">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="R17" s="39">
         <f>N17*O17*P17*Q17</f>
-        <v>168.2</v>
+        <v>336.4</v>
       </c>
       <c r="S17" s="9" t="n"/>
     </row>
@@ -7011,7 +7011,7 @@
       <c r="Q37" s="43" t="n"/>
       <c r="R37" s="19">
         <f>SUM(R17:R36)</f>
-        <v>168.2</v>
+        <v>336.4</v>
       </c>
       <c r="S37" s="9" t="n"/>
     </row>
@@ -12279,7 +12279,7 @@
       <c r="J17" s="45" t="n"/>
       <c r="K17" s="38" t="inlineStr">
         <is>
-          <t>Long. 4#3 (kg)</t>
+          <t>Long. 2 Ø1/2" (#4) vertical (kg)</t>
         </is>
       </c>
       <c r="L17" s="42" t="n"/>
@@ -12297,7 +12297,7 @@
         <v>1</v>
       </c>
       <c r="R17" s="39" t="n">
-        <v>376.8</v>
+        <v>668.8</v>
       </c>
       <c r="S17" s="9" t="n"/>
     </row>
@@ -12307,7 +12307,7 @@
       <c r="J18" s="45" t="n"/>
       <c r="K18" s="38" t="inlineStr">
         <is>
-          <t>Estribos #2 c/0.20 (kg)</t>
+          <t>Estribos/ganchos #2 (1/4") (kg)</t>
         </is>
       </c>
       <c r="L18" s="42" t="n"/>
@@ -12317,7 +12317,7 @@
       <c r="P18" s="39" t="n"/>
       <c r="Q18" s="39" t="n"/>
       <c r="R18" s="39" t="n">
-        <v>105.1</v>
+        <v>269.1</v>
       </c>
       <c r="S18" s="9" t="n"/>
     </row>
@@ -12337,7 +12337,7 @@
       <c r="P19" s="39" t="n"/>
       <c r="Q19" s="39" t="n"/>
       <c r="R19" s="39" t="n">
-        <v>481.9</v>
+        <v>937.9</v>
       </c>
       <c r="S19" s="9" t="n"/>
     </row>
@@ -12357,7 +12357,7 @@
       <c r="P20" s="39" t="n"/>
       <c r="Q20" s="39" t="n"/>
       <c r="R20" s="39" t="n">
-        <v>530.1</v>
+        <v>1031.7</v>
       </c>
       <c r="S20" s="9" t="n"/>
     </row>
@@ -12609,7 +12609,7 @@
       <c r="Q37" s="43" t="n"/>
       <c r="R37" s="19">
         <f>R20</f>
-        <v>530.1</v>
+        <v>1031.7</v>
       </c>
       <c r="S37" s="9" t="n"/>
     </row>
@@ -15728,7 +15728,7 @@
       <c r="J17" s="45" t="n"/>
       <c r="K17" s="38" t="inlineStr">
         <is>
-          <t>Excavacion masiva plataforma</t>
+          <t>Excavacion plataforma e=0.55</t>
         </is>
       </c>
       <c r="L17" s="42" t="n"/>
@@ -15755,14 +15755,29 @@
       <c r="A18" s="8" t="n"/>
       <c r="B18" s="44" t="n"/>
       <c r="J18" s="45" t="n"/>
-      <c r="K18" s="38" t="n"/>
+      <c r="K18" s="38" t="inlineStr">
+        <is>
+          <t>Zanjas cimentacion a 1.5m (extra 0.95)</t>
+        </is>
+      </c>
       <c r="L18" s="42" t="n"/>
       <c r="M18" s="43" t="n"/>
-      <c r="N18" s="39" t="n"/>
-      <c r="O18" s="39" t="n"/>
-      <c r="P18" s="39" t="n"/>
-      <c r="Q18" s="39" t="n"/>
-      <c r="R18" s="39" t="n"/>
+      <c r="N18" s="39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O18" s="39" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P18" s="39" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="Q18" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" s="39">
+        <f>N18*O18*P18*Q18</f>
+        <v>43.376999999999995</v>
+      </c>
       <c r="S18" s="9" t="n"/>
     </row>
     <row r="19" ht="15.6" customHeight="1">
@@ -16041,7 +16056,7 @@
       <c r="Q37" s="43" t="n"/>
       <c r="R37" s="19">
         <f>SUM(R17:R36)</f>
-        <v>118.914125</v>
+        <v>162.291125</v>
       </c>
       <c r="S37" s="9" t="n"/>
     </row>
@@ -16834,7 +16849,7 @@
       <c r="J17" s="45" t="n"/>
       <c r="K17" s="38" t="inlineStr">
         <is>
-          <t>Capa subbase bajo placa e=0.15</t>
+          <t>Colchon granular 0.30 m bajo placa</t>
         </is>
       </c>
       <c r="L17" s="42" t="n"/>
@@ -16843,7 +16858,7 @@
         <v>9.85</v>
       </c>
       <c r="O17" s="39" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="P17" s="39" t="n">
         <v>21.95</v>
@@ -16853,7 +16868,7 @@
       </c>
       <c r="R17" s="39">
         <f>N17*O17*P17*Q17</f>
-        <v>32.431124999999994</v>
+        <v>64.86224999999999</v>
       </c>
       <c r="S17" s="9" t="n"/>
     </row>
@@ -17147,7 +17162,7 @@
       <c r="Q37" s="43" t="n"/>
       <c r="R37" s="19">
         <f>SUM(R17:R36)</f>
-        <v>32.431124999999994</v>
+        <v>64.86224999999999</v>
       </c>
       <c r="S37" s="9" t="n"/>
     </row>
@@ -17940,26 +17955,26 @@
       <c r="J17" s="45" t="n"/>
       <c r="K17" s="38" t="inlineStr">
         <is>
-          <t>Zanjas vigas long. A,B</t>
+          <t>Afinado fondo de zanjas</t>
         </is>
       </c>
       <c r="L17" s="42" t="n"/>
       <c r="M17" s="43" t="n"/>
       <c r="N17" s="39" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O17" s="39" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="P17" s="39" t="n">
-        <v>19.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="Q17" s="39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17" s="39">
         <f>N17*O17*P17*Q17</f>
-        <v>6.336000000000001</v>
+        <v>6.848999999999999</v>
       </c>
       <c r="S17" s="9" t="n"/>
     </row>
@@ -17967,29 +17982,14 @@
       <c r="A18" s="8" t="n"/>
       <c r="B18" s="44" t="n"/>
       <c r="J18" s="45" t="n"/>
-      <c r="K18" s="38" t="inlineStr">
-        <is>
-          <t>Zanjas vigas transv. (luz libre)</t>
-        </is>
-      </c>
+      <c r="K18" s="38" t="n"/>
       <c r="L18" s="42" t="n"/>
       <c r="M18" s="43" t="n"/>
-      <c r="N18" s="39" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O18" s="39" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P18" s="39" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="Q18" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="R18" s="39">
-        <f>N18*O18*P18*Q18</f>
-        <v>5.840000000000001</v>
-      </c>
+      <c r="N18" s="39" t="n"/>
+      <c r="O18" s="39" t="n"/>
+      <c r="P18" s="39" t="n"/>
+      <c r="Q18" s="39" t="n"/>
+      <c r="R18" s="39" t="n"/>
       <c r="S18" s="9" t="n"/>
     </row>
     <row r="19" ht="15.6" customHeight="1">
@@ -18268,7 +18268,7 @@
       <c r="Q37" s="43" t="n"/>
       <c r="R37" s="19">
         <f>SUM(R17:R36)</f>
-        <v>12.176000000000002</v>
+        <v>6.848999999999999</v>
       </c>
       <c r="S37" s="9" t="n"/>
     </row>

--- a/Proyectos/Fundamentos-de-Construccion/Solucion/MEMORIAS DE CALCULO -FORMATO PROFESOR- DILIGENCIADO.xlsx
+++ b/Proyectos/Fundamentos-de-Construccion/Solucion/MEMORIAS DE CALCULO -FORMATO PROFESOR- DILIGENCIADO.xlsx
@@ -3350,26 +3350,26 @@
       <c r="J17" s="45" t="n"/>
       <c r="K17" s="38" t="inlineStr">
         <is>
-          <t>Columnas 0.40x0.40 h=4.90 (10 und)</t>
+          <t>Columnas 0.50x0.50 h=4.90 (4 und)</t>
         </is>
       </c>
       <c r="L17" s="42" t="n"/>
       <c r="M17" s="43" t="n"/>
       <c r="N17" s="39" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="O17" s="39" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="P17" s="39" t="n">
         <v>4.9</v>
       </c>
       <c r="Q17" s="39" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="R17" s="39">
         <f>N17*O17*P17*Q17</f>
-        <v>7.8400000000000025</v>
+        <v>4.9</v>
       </c>
       <c r="S17" s="9" t="n"/>
     </row>
@@ -3377,14 +3377,29 @@
       <c r="A18" s="8" t="n"/>
       <c r="B18" s="44" t="n"/>
       <c r="J18" s="45" t="n"/>
-      <c r="K18" s="38" t="n"/>
+      <c r="K18" s="38" t="inlineStr">
+        <is>
+          <t>Columnas 0.40x0.40 h=4.90 (4 und)</t>
+        </is>
+      </c>
       <c r="L18" s="42" t="n"/>
       <c r="M18" s="43" t="n"/>
-      <c r="N18" s="39" t="n"/>
-      <c r="O18" s="39" t="n"/>
-      <c r="P18" s="39" t="n"/>
-      <c r="Q18" s="39" t="n"/>
-      <c r="R18" s="39" t="n"/>
+      <c r="N18" s="39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O18" s="39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P18" s="39" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Q18" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="R18" s="39">
+        <f>N18*O18*P18*Q18</f>
+        <v>3.136000000000001</v>
+      </c>
       <c r="S18" s="9" t="n"/>
     </row>
     <row r="19" ht="15.6" customHeight="1">
@@ -3663,7 +3678,7 @@
       <c r="Q37" s="43" t="n"/>
       <c r="R37" s="19">
         <f>SUM(R17:R36)</f>
-        <v>7.8400000000000025</v>
+        <v>8.036000000000001</v>
       </c>
       <c r="S37" s="9" t="n"/>
     </row>
@@ -5577,7 +5592,7 @@
       <c r="J17" s="45" t="n"/>
       <c r="K17" s="38" t="inlineStr">
         <is>
-          <t>Area bruta muros (L=173.60 x H=2.90)</t>
+          <t>Area bruta muros (L=173.60 x H=3.00)</t>
         </is>
       </c>
       <c r="L17" s="42" t="n"/>
@@ -5589,14 +5604,14 @@
         <v>1</v>
       </c>
       <c r="P17" s="39" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="39" t="n">
         <v>1</v>
       </c>
       <c r="R17" s="39">
         <f>N17*O17*P17*Q17</f>
-        <v>503.43999999999994</v>
+        <v>520.8</v>
       </c>
       <c r="S17" s="9" t="n"/>
     </row>
@@ -5618,14 +5633,14 @@
         <v>1</v>
       </c>
       <c r="P18" s="39" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="39" t="n">
         <v>-0.2</v>
       </c>
       <c r="R18" s="39">
         <f>N18*O18*P18*Q18</f>
-        <v>-100.68799999999999</v>
+        <v>-104.16</v>
       </c>
       <c r="S18" s="9" t="n"/>
     </row>
@@ -5905,7 +5920,7 @@
       <c r="Q37" s="43" t="n"/>
       <c r="R37" s="19">
         <f>SUM(R17:R36)</f>
-        <v>402.75199999999995</v>
+        <v>416.64</v>
       </c>
       <c r="S37" s="9" t="n"/>
     </row>
@@ -6698,7 +6713,7 @@
       <c r="J17" s="45" t="n"/>
       <c r="K17" s="38" t="inlineStr">
         <is>
-          <t>Columnetas c/1.5m (116 und x H=2.90)</t>
+          <t>Columnetas c/1.5m (116 und x H=3.00)</t>
         </is>
       </c>
       <c r="L17" s="42" t="n"/>
@@ -6710,14 +6725,14 @@
         <v>1</v>
       </c>
       <c r="P17" s="39" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="39" t="n">
         <v>116</v>
       </c>
       <c r="R17" s="39">
         <f>N17*O17*P17*Q17</f>
-        <v>336.4</v>
+        <v>348.0</v>
       </c>
       <c r="S17" s="9" t="n"/>
     </row>
@@ -7011,7 +7026,7 @@
       <c r="Q37" s="43" t="n"/>
       <c r="R37" s="19">
         <f>SUM(R17:R36)</f>
-        <v>336.4</v>
+        <v>348.0</v>
       </c>
       <c r="S37" s="9" t="n"/>
     </row>
@@ -7810,7 +7825,7 @@
       <c r="L17" s="42" t="n"/>
       <c r="M17" s="43" t="n"/>
       <c r="N17" s="39" t="n">
-        <v>402.75</v>
+        <v>416.64</v>
       </c>
       <c r="O17" s="39" t="n">
         <v>1</v>
@@ -7823,7 +7838,7 @@
       </c>
       <c r="R17" s="39">
         <f>N17*O17*P17*Q17</f>
-        <v>261.7875</v>
+        <v>270.816</v>
       </c>
       <c r="S17" s="9" t="n"/>
     </row>
@@ -8117,7 +8132,7 @@
       <c r="Q37" s="43" t="n"/>
       <c r="R37" s="19">
         <f>SUM(R17:R36)</f>
-        <v>261.7875</v>
+        <v>270.816</v>
       </c>
       <c r="S37" s="9" t="n"/>
     </row>
@@ -10033,7 +10048,7 @@
       <c r="J17" s="45" t="n"/>
       <c r="K17" s="38" t="inlineStr">
         <is>
-          <t>Long. 10col x (2#6+2#7) L=5.95 (kg)</t>
+          <t>Long. 8 col x (2#6+2#7) L=5.95 (kg)</t>
         </is>
       </c>
       <c r="L17" s="42" t="n"/>
@@ -10051,7 +10066,7 @@
         <v>1</v>
       </c>
       <c r="R17" s="39" t="n">
-        <v>628</v>
+        <v>502.4</v>
       </c>
       <c r="S17" s="9" t="n"/>
     </row>
@@ -10061,7 +10076,7 @@
       <c r="J18" s="45" t="n"/>
       <c r="K18" s="38" t="inlineStr">
         <is>
-          <t>Estribos #2 c/0.20 (kg)</t>
+          <t>Estribos #2 c/0.20 (4 col 0.40 + 4 col 0.50) (kg)</t>
         </is>
       </c>
       <c r="L18" s="42" t="n"/>
@@ -10071,7 +10086,7 @@
       <c r="P18" s="39" t="n"/>
       <c r="Q18" s="39" t="n"/>
       <c r="R18" s="39" t="n">
-        <v>91.90000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="S18" s="9" t="n"/>
     </row>
@@ -10091,7 +10106,7 @@
       <c r="P19" s="39" t="n"/>
       <c r="Q19" s="39" t="n"/>
       <c r="R19" s="39" t="n">
-        <v>719.8</v>
+        <v>585.7</v>
       </c>
       <c r="S19" s="9" t="n"/>
     </row>
@@ -10111,7 +10126,7 @@
       <c r="P20" s="39" t="n"/>
       <c r="Q20" s="39" t="n"/>
       <c r="R20" s="39" t="n">
-        <v>791.8</v>
+        <v>644.2</v>
       </c>
       <c r="S20" s="9" t="n"/>
     </row>
@@ -10363,7 +10378,7 @@
       <c r="Q37" s="43" t="n"/>
       <c r="R37" s="19">
         <f>R20</f>
-        <v>791.8</v>
+        <v>644.2</v>
       </c>
       <c r="S37" s="9" t="n"/>
     </row>
@@ -12297,7 +12312,7 @@
         <v>1</v>
       </c>
       <c r="R17" s="39" t="n">
-        <v>668.8</v>
+        <v>691.8</v>
       </c>
       <c r="S17" s="9" t="n"/>
     </row>
@@ -12317,7 +12332,7 @@
       <c r="P18" s="39" t="n"/>
       <c r="Q18" s="39" t="n"/>
       <c r="R18" s="39" t="n">
-        <v>269.1</v>
+        <v>278.4</v>
       </c>
       <c r="S18" s="9" t="n"/>
     </row>
@@ -12337,7 +12352,7 @@
       <c r="P19" s="39" t="n"/>
       <c r="Q19" s="39" t="n"/>
       <c r="R19" s="39" t="n">
-        <v>937.9</v>
+        <v>970.2</v>
       </c>
       <c r="S19" s="9" t="n"/>
     </row>
@@ -12357,7 +12372,7 @@
       <c r="P20" s="39" t="n"/>
       <c r="Q20" s="39" t="n"/>
       <c r="R20" s="39" t="n">
-        <v>1031.7</v>
+        <v>1067.2</v>
       </c>
       <c r="S20" s="9" t="n"/>
     </row>
@@ -12609,7 +12624,7 @@
       <c r="Q37" s="43" t="n"/>
       <c r="R37" s="19">
         <f>R20</f>
-        <v>1031.7</v>
+        <v>1067.2</v>
       </c>
       <c r="S37" s="9" t="n"/>
     </row>
@@ -15728,26 +15743,26 @@
       <c r="J17" s="45" t="n"/>
       <c r="K17" s="38" t="inlineStr">
         <is>
-          <t>Excavacion plataforma e=0.55</t>
+          <t>Pozos zapatas Z-1 (2.30x2.30) a 1.5m</t>
         </is>
       </c>
       <c r="L17" s="42" t="n"/>
       <c r="M17" s="43" t="n"/>
       <c r="N17" s="39" t="n">
-        <v>9.85</v>
+        <v>2.3</v>
       </c>
       <c r="O17" s="39" t="n">
-        <v>0.55</v>
+        <v>2.3</v>
       </c>
       <c r="P17" s="39" t="n">
-        <v>21.95</v>
+        <v>1.5</v>
       </c>
       <c r="Q17" s="39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R17" s="39">
         <f>N17*O17*P17*Q17</f>
-        <v>118.914125</v>
+        <v>31.739999999999995</v>
       </c>
       <c r="S17" s="9" t="n"/>
     </row>
@@ -15757,26 +15772,26 @@
       <c r="J18" s="45" t="n"/>
       <c r="K18" s="38" t="inlineStr">
         <is>
-          <t>Zanjas cimentacion a 1.5m (extra 0.95)</t>
+          <t>Pozos zapatas Z-2 (2.15x2.15) a 1.5m</t>
         </is>
       </c>
       <c r="L18" s="42" t="n"/>
       <c r="M18" s="43" t="n"/>
       <c r="N18" s="39" t="n">
-        <v>0.6</v>
+        <v>2.15</v>
       </c>
       <c r="O18" s="39" t="n">
-        <v>0.95</v>
+        <v>2.15</v>
       </c>
       <c r="P18" s="39" t="n">
-        <v>76.09999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="Q18" s="39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R18" s="39">
         <f>N18*O18*P18*Q18</f>
-        <v>43.376999999999995</v>
+        <v>27.735</v>
       </c>
       <c r="S18" s="9" t="n"/>
     </row>
@@ -15784,14 +15799,29 @@
       <c r="A19" s="8" t="n"/>
       <c r="B19" s="44" t="n"/>
       <c r="J19" s="45" t="n"/>
-      <c r="K19" s="38" t="n"/>
+      <c r="K19" s="38" t="inlineStr">
+        <is>
+          <t>Zanjas de vigas a 1.5m</t>
+        </is>
+      </c>
       <c r="L19" s="42" t="n"/>
       <c r="M19" s="43" t="n"/>
-      <c r="N19" s="39" t="n"/>
-      <c r="O19" s="39" t="n"/>
-      <c r="P19" s="39" t="n"/>
-      <c r="Q19" s="39" t="n"/>
-      <c r="R19" s="39" t="n"/>
+      <c r="N19" s="39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O19" s="39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P19" s="39" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="Q19" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" s="39">
+        <f>N19*O19*P19*Q19</f>
+        <v>52.64999999999999</v>
+      </c>
       <c r="S19" s="9" t="n"/>
     </row>
     <row r="20" ht="15.6" customHeight="1">
@@ -16056,7 +16086,7 @@
       <c r="Q37" s="43" t="n"/>
       <c r="R37" s="19">
         <f>SUM(R17:R36)</f>
-        <v>162.291125</v>
+        <v>112.12499999999999</v>
       </c>
       <c r="S37" s="9" t="n"/>
     </row>
@@ -17955,26 +17985,26 @@
       <c r="J17" s="45" t="n"/>
       <c r="K17" s="38" t="inlineStr">
         <is>
-          <t>Afinado fondo de zanjas</t>
+          <t>Afinado fondo de pozos y zanjas e=0.10</t>
         </is>
       </c>
       <c r="L17" s="42" t="n"/>
       <c r="M17" s="43" t="n"/>
       <c r="N17" s="39" t="n">
-        <v>0.6</v>
+        <v>74.75</v>
       </c>
       <c r="O17" s="39" t="n">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="P17" s="39" t="n">
-        <v>76.09999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="Q17" s="39" t="n">
         <v>1</v>
       </c>
       <c r="R17" s="39">
         <f>N17*O17*P17*Q17</f>
-        <v>6.848999999999999</v>
+        <v>7.4750000000000005</v>
       </c>
       <c r="S17" s="9" t="n"/>
     </row>
@@ -18268,7 +18298,7 @@
       <c r="Q37" s="43" t="n"/>
       <c r="R37" s="19">
         <f>SUM(R17:R36)</f>
-        <v>6.848999999999999</v>
+        <v>7.4750000000000005</v>
       </c>
       <c r="S37" s="9" t="n"/>
     </row>
